--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251014_201619.xlsx
@@ -5178,7 +5178,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
